--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705BACDB-8E5F-4650-BD7D-CAE6854CD977}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{975AF494-F2F5-4058-96CF-8B53E0BD6053}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -308,12 +308,131 @@
     <t>18/12/2025</t>
   </si>
   <si>
-    <t>Nationalization-CR42-7033766317.pdf</t>
-  </si>
-  <si>
     <t>CR42</t>
   </si>
   <si>
+    <t>Chamber Membership Certificate</t>
+  </si>
+  <si>
+    <t>Riyadh Chamber</t>
+  </si>
+  <si>
+    <t>COC Riyadh Chamber – CR32</t>
+  </si>
+  <si>
+    <t>شهادة عضوية غرفة الرياض</t>
+  </si>
+  <si>
+    <t>الغرفة التجارية الصناعية بالرياض</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم العضوية</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 742640</t>
+    </r>
+  </si>
+  <si>
+    <t>18/07/2022</t>
+  </si>
+  <si>
+    <t>Meric -CoC Membership Certificate EXP May 25 2026.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CR: 1010813032 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>درجة ثانية</t>
+    </r>
+  </si>
+  <si>
+    <t>Commercial Registration Certificate</t>
+  </si>
+  <si>
+    <t>Ministry of Commerce</t>
+  </si>
+  <si>
+    <t>CR 32</t>
+  </si>
+  <si>
+    <t>No expiry visible on face.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">السجل التجاري – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>CR32</t>
+    </r>
+  </si>
+  <si>
+    <t>وزارة التجارة</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم السجل التجاري</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 1010813032</t>
+    </r>
+  </si>
+  <si>
+    <t>07/07/2022</t>
+  </si>
+  <si>
+    <t>CR32-Main-1010813032.pdf</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -330,6 +449,419 @@
         <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">: 7029908865 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">فرع شركة أجنبية </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>نشطة</t>
+    </r>
+  </si>
+  <si>
+    <t>TVTC License</t>
+  </si>
+  <si>
+    <t>TVTC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ترخيص التدريب – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>TVTC</t>
+    </r>
+  </si>
+  <si>
+    <t>المؤسسة العامة للتدريب التقني والمهني</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الإصدار</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 1181861142</t>
+    </r>
+  </si>
+  <si>
+    <t>TVTC-License-2028.pdf</t>
+  </si>
+  <si>
+    <t>مركز ميرك للتدريب – الرياض</t>
+  </si>
+  <si>
+    <t>مقيم</t>
+  </si>
+  <si>
+    <t>تأشيرة</t>
+  </si>
+  <si>
+    <t>تفاصيل - مقيم.xlsx</t>
+  </si>
+  <si>
+    <t>حالة التأشيرة: غبر مستعمل - السفر قبل</t>
+  </si>
+  <si>
+    <t>إقامة</t>
+  </si>
+  <si>
+    <t>مريم ايهاب محمود احمد همام</t>
+  </si>
+  <si>
+    <t>إقامة مريم ايهاب محمود احمد همام</t>
+  </si>
+  <si>
+    <t>رقم الإقامة: 2583134610</t>
+  </si>
+  <si>
+    <t>SME Certificate</t>
+  </si>
+  <si>
+    <t>SME</t>
+  </si>
+  <si>
+    <t>SME – CR42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">شهادة </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>SME</t>
+    </r>
+  </si>
+  <si>
+    <t>الهيئة العامة للمنشآت الصغيرة والمتوسطة</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 26217343650</t>
+    </r>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>SME - CR42.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 7033766317</t>
+    </r>
+  </si>
+  <si>
+    <t>LINA AL ASHKAR</t>
+  </si>
+  <si>
+    <t>تأشيرة LINA AL ASHKAR</t>
+  </si>
+  <si>
+    <t>GOSI Certificate</t>
+  </si>
+  <si>
+    <t>GOSI</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">شهادة </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GOSI – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>التأمينات</t>
+    </r>
+  </si>
+  <si>
+    <t>المؤسسة العامة للتأمينات الاجتماعية</t>
+  </si>
+  <si>
+    <t>11/04/2026</t>
+  </si>
+  <si>
+    <t>MOHAMMED NAYAL</t>
+  </si>
+  <si>
+    <t>تأشيرة MOHAMMED NAYAL</t>
+  </si>
+  <si>
+    <t>حالة التأشيرة: مستعمل</t>
+  </si>
+  <si>
+    <t>National Address Record</t>
+  </si>
+  <si>
+    <t>SPL</t>
+  </si>
+  <si>
+    <t>National address 42</t>
+  </si>
+  <si>
+    <t>العنوان الوطني</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">البريد السعودي </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>SPL</t>
+    </r>
+  </si>
+  <si>
+    <t>3/2/2026</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RUQA7523 – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>سعيد بن زيد، حي قرطبة، الرياض</t>
+    </r>
+  </si>
+  <si>
+    <t>COC Riyadh Chamber – CR42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم العضوية</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 836599</t>
+    </r>
+  </si>
+  <si>
+    <t>16/07/2023</t>
+  </si>
+  <si>
+    <t>CoC 42 EXP Jan 6 2027.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CR: 1010860142 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>درجة ثانية</t>
+    </r>
+  </si>
+  <si>
+    <t>CR 42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">السجل التجاري – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>CR42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم السجل التجاري</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 1010860142</t>
+    </r>
+  </si>
+  <si>
+    <t>08/02/2023</t>
+  </si>
+  <si>
+    <t>CR42-Center-1010860142.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">: 7033766317 · </t>
     </r>
     <r>
@@ -339,6 +871,344 @@
         <rFont val="FreeSans"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">فرع شركة أجنبية </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>نشطة</t>
+    </r>
+  </si>
+  <si>
+    <t>Investment License</t>
+  </si>
+  <si>
+    <t>Ministry of Investment</t>
+  </si>
+  <si>
+    <t>Services Investment License</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ترخيص الاستثمار – </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>MISA</t>
+    </r>
+  </si>
+  <si>
+    <t>وزارة الاستثمار</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الترخيص</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 102164308134617</t>
+    </r>
+  </si>
+  <si>
+    <t>13/03/2022</t>
+  </si>
+  <si>
+    <t>MISA (New) - 2027.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 7029908865</t>
+    </r>
+  </si>
+  <si>
+    <t>إقامة LINA AL ASHKAR</t>
+  </si>
+  <si>
+    <t>رقم الإقامة: 2598378632</t>
+  </si>
+  <si>
+    <t>إقامة MOHAMMED NAYAL</t>
+  </si>
+  <si>
+    <t>رقم الإقامة: 2572607188</t>
+  </si>
+  <si>
+    <t>National address 32</t>
+  </si>
+  <si>
+    <t>تأشيرة مريم ايهاب محمود احمد همام</t>
+  </si>
+  <si>
+    <t>MOSI Certificate</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>SME – CR32</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 26265343654</t>
+    </r>
+  </si>
+  <si>
+    <t>SME - CR32.pdf</t>
+  </si>
+  <si>
+    <t>دليل استيراد Power BI</t>
+  </si>
+  <si>
+    <t>١</t>
+  </si>
+  <si>
+    <t>افتح Power BI Desktop → Home → Get Data → Excel Workbook</t>
+  </si>
+  <si>
+    <t>٢</t>
+  </si>
+  <si>
+    <t>اختر هذا الملف، ثم حدد ورقة Tracker_All فقط → Load</t>
+  </si>
+  <si>
+    <t>٣</t>
+  </si>
+  <si>
+    <t>Transform Data: تأكد أن عمود [تاريخ الانتهاء] نوعه Date</t>
+  </si>
+  <si>
+    <t>٤</t>
+  </si>
+  <si>
+    <t>تأكد أن [الأيام المتبقية] نوعه Whole Number</t>
+  </si>
+  <si>
+    <t>٥</t>
+  </si>
+  <si>
+    <t>أغلق Power Query Editor → Apply</t>
+  </si>
+  <si>
+    <t>المقاييس – انسخها من ملف DAX_Measures.txt</t>
+  </si>
+  <si>
+    <t>تصميم اللوحة – راجع ملف PowerBI_Design_Guide.pdf</t>
+  </si>
+  <si>
+    <t>تحديث البيانات: كلما عدّلت هذا الملف، اضغط Refresh في Power BI</t>
+  </si>
+  <si>
+    <t>مسار الملف: لا تغير اسم الملف أو مساره بعد ربطه بـ Power BI</t>
+  </si>
+  <si>
+    <t>GOSI 42</t>
+  </si>
+  <si>
+    <r>
+      <t>رقم الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 256343-19899920</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>رقم الإثبات</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 1080130933</t>
+    </r>
+  </si>
+  <si>
+    <t>رقم الإثبات: 1090961124</t>
+  </si>
+  <si>
+    <t>Address Meirc Consulting Training.pdf</t>
+  </si>
+  <si>
+    <t>Address Meirc Training Center.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GOSI CR42 11-25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>.pdf</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>رمز الشهادة</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: 119567603</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>رقم الاشتراك</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 638909642 · 9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
+      <t>مشتركين</t>
+    </r>
+  </si>
+  <si>
+    <t>رقم الشهادة : 318666 M</t>
+  </si>
+  <si>
+    <t>Local Content Certificate.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 318666 M</t>
+  </si>
+  <si>
+    <t>هيئة المحتوى المحلي والمشتريات الحكومية</t>
+  </si>
+  <si>
+    <t>شهادة المحتوى المحلي - Local Content Certificate</t>
+  </si>
+  <si>
+    <t>Local Content &amp; Government Procurement Authority</t>
+  </si>
+  <si>
+    <t>Local Content Certificate</t>
+  </si>
+  <si>
+    <t>Local Content</t>
+  </si>
+  <si>
+    <t>Nationalization Certificate -CR42- Expiring Dec 6th.pdf</t>
+  </si>
+  <si>
+    <r>
+      <t>الرقم الوطني</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 7033766317 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="FreeSans"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">توطين </t>
     </r>
     <r>
@@ -348,884 +1218,8 @@
         <rFont val="Calibri"/>
         <charset val="1"/>
       </rPr>
-      <t>55%</t>
-    </r>
-  </si>
-  <si>
-    <t>Chamber Membership Certificate</t>
-  </si>
-  <si>
-    <t>Riyadh Chamber</t>
-  </si>
-  <si>
-    <t>COC Riyadh Chamber – CR32</t>
-  </si>
-  <si>
-    <t>شهادة عضوية غرفة الرياض</t>
-  </si>
-  <si>
-    <t>الغرفة التجارية الصناعية بالرياض</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم العضوية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 742640</t>
-    </r>
-  </si>
-  <si>
-    <t>18/07/2022</t>
-  </si>
-  <si>
-    <t>Meric -CoC Membership Certificate EXP May 25 2026.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CR: 1010813032 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>درجة ثانية</t>
-    </r>
-  </si>
-  <si>
-    <t>Commercial Registration Certificate</t>
-  </si>
-  <si>
-    <t>Ministry of Commerce</t>
-  </si>
-  <si>
-    <t>CR 32</t>
-  </si>
-  <si>
-    <t>No expiry visible on face.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">السجل التجاري – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>CR32</t>
-    </r>
-  </si>
-  <si>
-    <t>وزارة التجارة</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم السجل التجاري</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 1010813032</t>
-    </r>
-  </si>
-  <si>
-    <t>07/07/2022</t>
-  </si>
-  <si>
-    <t>CR32-Main-1010813032.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 7029908865 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">فرع شركة أجنبية </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>نشطة</t>
-    </r>
-  </si>
-  <si>
-    <t>TVTC License</t>
-  </si>
-  <si>
-    <t>TVTC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ترخيص التدريب – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>TVTC</t>
-    </r>
-  </si>
-  <si>
-    <t>المؤسسة العامة للتدريب التقني والمهني</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الإصدار</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 1181861142</t>
-    </r>
-  </si>
-  <si>
-    <t>TVTC-License-2028.pdf</t>
-  </si>
-  <si>
-    <t>مركز ميرك للتدريب – الرياض</t>
-  </si>
-  <si>
-    <t>مقيم</t>
-  </si>
-  <si>
-    <t>تأشيرة</t>
-  </si>
-  <si>
-    <t>تفاصيل - مقيم.xlsx</t>
-  </si>
-  <si>
-    <t>حالة التأشيرة: غبر مستعمل - السفر قبل</t>
-  </si>
-  <si>
-    <t>إقامة</t>
-  </si>
-  <si>
-    <t>مريم ايهاب محمود احمد همام</t>
-  </si>
-  <si>
-    <t>إقامة مريم ايهاب محمود احمد همام</t>
-  </si>
-  <si>
-    <t>رقم الإقامة: 2583134610</t>
-  </si>
-  <si>
-    <t>SME Certificate</t>
-  </si>
-  <si>
-    <t>SME</t>
-  </si>
-  <si>
-    <t>SME – CR42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">شهادة </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>SME</t>
-    </r>
-  </si>
-  <si>
-    <t>الهيئة العامة للمنشآت الصغيرة والمتوسطة</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 26217343650</t>
-    </r>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>SME - CR42.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 7033766317</t>
-    </r>
-  </si>
-  <si>
-    <t>LINA AL ASHKAR</t>
-  </si>
-  <si>
-    <t>تأشيرة LINA AL ASHKAR</t>
-  </si>
-  <si>
-    <t>GOSI Certificate</t>
-  </si>
-  <si>
-    <t>GOSI</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">شهادة </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">GOSI – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>التأمينات</t>
-    </r>
-  </si>
-  <si>
-    <t>المؤسسة العامة للتأمينات الاجتماعية</t>
-  </si>
-  <si>
-    <t>11/04/2026</t>
-  </si>
-  <si>
-    <t>MOHAMMED NAYAL</t>
-  </si>
-  <si>
-    <t>تأشيرة MOHAMMED NAYAL</t>
-  </si>
-  <si>
-    <t>حالة التأشيرة: مستعمل</t>
-  </si>
-  <si>
-    <t>National Address Record</t>
-  </si>
-  <si>
-    <t>SPL</t>
-  </si>
-  <si>
-    <t>National address 42</t>
-  </si>
-  <si>
-    <t>العنوان الوطني</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">البريد السعودي </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>SPL</t>
-    </r>
-  </si>
-  <si>
-    <t>3/2/2026</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RUQA7523 – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>سعيد بن زيد، حي قرطبة، الرياض</t>
-    </r>
-  </si>
-  <si>
-    <t>COC Riyadh Chamber – CR42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم العضوية</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 836599</t>
-    </r>
-  </si>
-  <si>
-    <t>16/07/2023</t>
-  </si>
-  <si>
-    <t>CoC 42 EXP Jan 6 2027.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CR: 1010860142 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>درجة ثانية</t>
-    </r>
-  </si>
-  <si>
-    <t>CR 42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">السجل التجاري – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>CR42</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم السجل التجاري</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 1010860142</t>
-    </r>
-  </si>
-  <si>
-    <t>08/02/2023</t>
-  </si>
-  <si>
-    <t>CR42-Center-1010860142.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 7033766317 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">فرع شركة أجنبية </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>نشطة</t>
-    </r>
-  </si>
-  <si>
-    <t>Investment License</t>
-  </si>
-  <si>
-    <t>Ministry of Investment</t>
-  </si>
-  <si>
-    <t>Services Investment License</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ترخيص الاستثمار – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>MISA</t>
-    </r>
-  </si>
-  <si>
-    <t>وزارة الاستثمار</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الترخيص</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 102164308134617</t>
-    </r>
-  </si>
-  <si>
-    <t>13/03/2022</t>
-  </si>
-  <si>
-    <t>MISA (New) - 2027.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>الرقم الوطني</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 7029908865</t>
-    </r>
-  </si>
-  <si>
-    <t>إقامة LINA AL ASHKAR</t>
-  </si>
-  <si>
-    <t>رقم الإقامة: 2598378632</t>
-  </si>
-  <si>
-    <t>إقامة MOHAMMED NAYAL</t>
-  </si>
-  <si>
-    <t>رقم الإقامة: 2572607188</t>
-  </si>
-  <si>
-    <t>National address 32</t>
-  </si>
-  <si>
-    <t>تأشيرة مريم ايهاب محمود احمد همام</t>
-  </si>
-  <si>
-    <t>MOSI Certificate</t>
-  </si>
-  <si>
-    <t>MOSI</t>
-  </si>
-  <si>
-    <t>SME – CR32</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 26265343654</t>
-    </r>
-  </si>
-  <si>
-    <t>SME - CR32.pdf</t>
-  </si>
-  <si>
-    <t>دليل استيراد Power BI</t>
-  </si>
-  <si>
-    <t>١</t>
-  </si>
-  <si>
-    <t>افتح Power BI Desktop → Home → Get Data → Excel Workbook</t>
-  </si>
-  <si>
-    <t>٢</t>
-  </si>
-  <si>
-    <t>اختر هذا الملف، ثم حدد ورقة Tracker_All فقط → Load</t>
-  </si>
-  <si>
-    <t>٣</t>
-  </si>
-  <si>
-    <t>Transform Data: تأكد أن عمود [تاريخ الانتهاء] نوعه Date</t>
-  </si>
-  <si>
-    <t>٤</t>
-  </si>
-  <si>
-    <t>تأكد أن [الأيام المتبقية] نوعه Whole Number</t>
-  </si>
-  <si>
-    <t>٥</t>
-  </si>
-  <si>
-    <t>أغلق Power Query Editor → Apply</t>
-  </si>
-  <si>
-    <t>المقاييس – انسخها من ملف DAX_Measures.txt</t>
-  </si>
-  <si>
-    <t>تصميم اللوحة – راجع ملف PowerBI_Design_Guide.pdf</t>
-  </si>
-  <si>
-    <t>تحديث البيانات: كلما عدّلت هذا الملف، اضغط Refresh في Power BI</t>
-  </si>
-  <si>
-    <t>مسار الملف: لا تغير اسم الملف أو مساره بعد ربطه بـ Power BI</t>
-  </si>
-  <si>
-    <t>GOSI 42</t>
-  </si>
-  <si>
-    <r>
-      <t>رقم الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 256343-19899920</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>رقم الإثبات</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 1080130933</t>
-    </r>
-  </si>
-  <si>
-    <t>رقم الإثبات: 1090961124</t>
-  </si>
-  <si>
-    <t>Address Meirc Consulting Training.pdf</t>
-  </si>
-  <si>
-    <t>Address Meirc Training Center.pdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>GOSI CR42 11-25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>.pdf</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>رمز الشهادة</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t>: 119567603</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>رقم الاشتراك</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 638909642 · 9 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="FreeSans"/>
-        <family val="2"/>
-      </rPr>
-      <t>مشتركين</t>
-    </r>
-  </si>
-  <si>
-    <t>رقم الشهادة : 318666 M</t>
-  </si>
-  <si>
-    <t>Local Content Certificate.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 318666 M</t>
-  </si>
-  <si>
-    <t>هيئة المحتوى المحلي والمشتريات الحكومية</t>
-  </si>
-  <si>
-    <t>شهادة المحتوى المحلي - Local Content Certificate</t>
-  </si>
-  <si>
-    <t>Local Content &amp; Government Procurement Authority</t>
-  </si>
-  <si>
-    <t>Local Content Certificate</t>
-  </si>
-  <si>
-    <t>Local Content</t>
+      <t>71%</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1750,7 +1744,7 @@
       </c>
       <c r="F2" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:G20" si="0">IF(E2="","",E2-30)</f>
@@ -1808,7 +1802,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="0"/>
@@ -1864,23 +1858,23 @@
         <v>39</v>
       </c>
       <c r="E4" s="4">
-        <v>46295</v>
+        <v>46362</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>46265</v>
+        <v>46332</v>
       </c>
       <c r="H4" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I4" s="6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>21</v>
@@ -1895,19 +1889,19 @@
         <v>34</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O4" t="s">
         <v>40</v>
       </c>
       <c r="P4" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q4" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" t="s">
-        <v>42</v>
-      </c>
       <c r="R4" s="7" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="14.25" customHeight="1">
@@ -1915,20 +1909,20 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="E5" s="4">
         <v>46532</v>
       </c>
       <c r="F5" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
@@ -1949,25 +1943,25 @@
         <v>32</v>
       </c>
       <c r="L5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="O5" t="s">
         <v>48</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="P5" t="s">
         <v>49</v>
-      </c>
-      <c r="O5" t="s">
-        <v>50</v>
-      </c>
-      <c r="P5" t="s">
-        <v>51</v>
       </c>
       <c r="Q5" t="s">
         <v>27</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="24.75" customHeight="1">
@@ -1975,20 +1969,20 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="E6" s="4">
         <v>46532</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
@@ -2006,28 +2000,28 @@
         <v>21</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="N6" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="O6" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="P6" t="s">
         <v>59</v>
-      </c>
-      <c r="O6" t="s">
-        <v>60</v>
-      </c>
-      <c r="P6" t="s">
-        <v>61</v>
       </c>
       <c r="Q6" t="s">
         <v>27</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="14.25" customHeight="1">
@@ -2035,20 +2029,20 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="4">
         <v>46951</v>
       </c>
       <c r="F7" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
@@ -2067,22 +2061,22 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="P7" t="s">
         <v>66</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="Q7" t="s">
+        <v>41</v>
+      </c>
+      <c r="R7" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="P7" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="14.25" customHeight="1">
@@ -2090,20 +2084,20 @@
         <v>18</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="E8" s="9">
         <v>46526</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
@@ -2124,46 +2118,46 @@
         <v>32</v>
       </c>
       <c r="L8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="O8" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="P8" t="s">
         <v>83</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
+        <v>41</v>
+      </c>
+      <c r="R8" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="P8" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>42</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="14.25" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" s="9">
         <v>46452</v>
       </c>
       <c r="F9" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G9" s="4">
         <f t="shared" si="0"/>
@@ -2178,10 +2172,10 @@
         <v>منخفضة</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="14.25" customHeight="1">
@@ -2189,20 +2183,20 @@
         <v>18</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E10" s="10">
         <v>46351</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G10" s="4">
         <f t="shared" si="0"/>
@@ -2221,46 +2215,46 @@
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O10" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="O10" t="s">
-        <v>93</v>
-      </c>
       <c r="P10" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R10" s="7" t="s">
         <v>156</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>42</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="14.25" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E11" s="10">
         <v>46469</v>
       </c>
       <c r="F11" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="0"/>
@@ -2275,10 +2269,10 @@
         <v>منخفضة</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
@@ -2286,20 +2280,20 @@
         <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E12" s="10">
         <v>46419</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" ref="G12" si="3">IF(E12="","",E12-30)</f>
@@ -2318,25 +2312,25 @@
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="O12" t="s">
         <v>100</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="O12" t="s">
-        <v>102</v>
-      </c>
       <c r="P12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
       </c>
       <c r="R12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
@@ -2344,20 +2338,20 @@
         <v>18</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="E13" s="10">
         <v>46419</v>
       </c>
       <c r="F13" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="0"/>
@@ -2376,25 +2370,25 @@
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="O13" t="s">
         <v>100</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="P13" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>41</v>
+      </c>
+      <c r="R13" t="s">
         <v>101</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="O13" t="s">
-        <v>102</v>
-      </c>
-      <c r="P13" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>42</v>
-      </c>
-      <c r="R13" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
@@ -2402,20 +2396,20 @@
         <v>18</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E14" s="10">
         <v>46391</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="0"/>
@@ -2436,25 +2430,25 @@
         <v>32</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="O14" t="s">
+        <v>104</v>
+      </c>
+      <c r="P14" t="s">
         <v>105</v>
       </c>
-      <c r="O14" t="s">
+      <c r="Q14" t="s">
+        <v>41</v>
+      </c>
+      <c r="R14" t="s">
         <v>106</v>
-      </c>
-      <c r="P14" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>42</v>
-      </c>
-      <c r="R14" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="24.75" customHeight="1">
@@ -2462,20 +2456,20 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" s="10">
         <v>46391</v>
       </c>
       <c r="F15" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="0"/>
@@ -2493,28 +2487,28 @@
         <v>21</v>
       </c>
       <c r="K15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="N15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="O15" t="s">
         <v>110</v>
       </c>
-      <c r="M15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N15" s="7" t="s">
+      <c r="P15" t="s">
         <v>111</v>
       </c>
-      <c r="O15" t="s">
+      <c r="Q15" t="s">
+        <v>41</v>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="P15" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>42</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
@@ -2522,20 +2516,20 @@
         <v>18</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="E16" s="10">
         <v>46396</v>
       </c>
       <c r="F16" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="0"/>
@@ -2556,46 +2550,46 @@
         <v>32</v>
       </c>
       <c r="L16" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="N16" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="O16" t="s">
         <v>119</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="P16" t="s">
         <v>120</v>
-      </c>
-      <c r="O16" t="s">
-        <v>121</v>
-      </c>
-      <c r="P16" t="s">
-        <v>122</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="14.25" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E17" s="10">
         <v>46535</v>
       </c>
       <c r="F17" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="0"/>
@@ -2610,31 +2604,31 @@
         <v>منخفضة</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E18" s="10">
         <v>46554</v>
       </c>
       <c r="F18" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="0"/>
@@ -2649,10 +2643,10 @@
         <v>منخفضة</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="14.25" customHeight="1">
@@ -2660,20 +2654,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E19" s="10">
         <v>46398</v>
       </c>
       <c r="F19" s="5">
         <f ca="1">E19-TODAY()</f>
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="0"/>
@@ -2699,20 +2693,20 @@
         <v>18</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E20" s="9">
         <v>46526</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">E20-TODAY()</f>
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="0"/>
@@ -2733,25 +2727,25 @@
         <v>32</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="O20" t="s">
         <v>82</v>
       </c>
-      <c r="N20" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="O20" t="s">
-        <v>84</v>
-      </c>
       <c r="P20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1">
@@ -2759,20 +2753,20 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="E21" s="4">
         <v>46599</v>
       </c>
       <c r="F21" s="5">
         <f ca="1">E21-TODAY()</f>
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" ref="G21" si="5">IF(E21="","",E21-30)</f>
@@ -2791,22 +2785,22 @@
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
       </c>
       <c r="R21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2834,7 +2828,7 @@
     <row r="2" spans="1:2" ht="14.25" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1">
@@ -2843,42 +2837,42 @@
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1">
@@ -2888,7 +2882,7 @@
     <row r="10" spans="1:2" ht="14.25" customHeight="1">
       <c r="A10" s="13"/>
       <c r="B10" s="16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1">
@@ -2898,7 +2892,7 @@
     <row r="12" spans="1:2" ht="14.25" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1">
@@ -2908,7 +2902,7 @@
     <row r="14" spans="1:2" ht="14.25" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.25" customHeight="1">
@@ -2918,21 +2912,21 @@
     <row r="16" spans="1:2" ht="14.25" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="E19" s="9">
         <v>46529</v>
@@ -2954,24 +2948,24 @@
         <v>#VALUE!</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E20" s="10">
         <v>46215</v>
@@ -2993,10 +2987,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Tracker_PowerBI_xlsx.xlsx
+++ b/Tracker_PowerBI_xlsx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meirc-my.sharepoint.com/personal/halzaben_meirc_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{975AF494-F2F5-4058-96CF-8B53E0BD6053}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{A9DB5D68-FAF6-475D-815D-D63DA13F66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D296A95-32C5-491C-A1AC-DDF209E0FC16}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1425" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker_All" sheetId="1" r:id="rId1"/>
@@ -261,9 +261,6 @@
     <t>07/05/2026</t>
   </si>
   <si>
-    <t>Nationalization-CR32-7029908865.pdf</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1220,6 +1217,9 @@
       </rPr>
       <t>71%</t>
     </r>
+  </si>
+  <si>
+    <t>Meirc 32 Nationalization Saudization Certificate EXP Jan1st 2027.pdf</t>
   </si>
 </sst>
 </file>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="F2" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="G2" s="4">
         <f t="shared" ref="G2:G20" si="0">IF(E2="","",E2-30)</f>
@@ -1798,23 +1798,23 @@
         <v>31</v>
       </c>
       <c r="E3" s="4">
-        <v>46295</v>
+        <v>46388</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="G3" s="4">
         <f t="shared" si="0"/>
-        <v>46265</v>
+        <v>46358</v>
       </c>
       <c r="H3" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>حرج</v>
+        <v>ساري</v>
       </c>
       <c r="I3" s="6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>عالية</v>
+        <v>منخفضة</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>21</v>
@@ -1835,13 +1835,13 @@
         <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="Q3" t="s">
         <v>27</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="14.25" customHeight="1">
@@ -1855,14 +1855,14 @@
         <v>30</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="4">
         <v>46362</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="H4" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I4" s="6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>21</v>
@@ -1889,19 +1889,19 @@
         <v>34</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q4" t="s">
         <v>40</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" s="7" t="s">
         <v>165</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="14.25" customHeight="1">
@@ -1909,20 +1909,20 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="E5" s="4">
         <v>46532</v>
       </c>
       <c r="F5" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
@@ -1943,25 +1943,25 @@
         <v>32</v>
       </c>
       <c r="L5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="O5" t="s">
         <v>47</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>48</v>
-      </c>
-      <c r="P5" t="s">
-        <v>49</v>
       </c>
       <c r="Q5" t="s">
         <v>27</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="24.75" customHeight="1">
@@ -1969,20 +1969,20 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E6" s="4">
         <v>46532</v>
       </c>
       <c r="F6" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
@@ -2000,28 +2000,28 @@
         <v>21</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="N6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="O6" t="s">
         <v>57</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>58</v>
-      </c>
-      <c r="P6" t="s">
-        <v>59</v>
       </c>
       <c r="Q6" t="s">
         <v>27</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="14.25" customHeight="1">
@@ -2029,20 +2029,20 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" s="4">
         <v>46951</v>
       </c>
       <c r="F7" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>678</v>
+        <v>649</v>
       </c>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="N7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="P7" t="s">
         <v>65</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="14.25" customHeight="1">
@@ -2084,20 +2084,20 @@
         <v>18</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="E8" s="9">
         <v>46526</v>
       </c>
       <c r="F8" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="G8" s="4">
         <f t="shared" si="0"/>
@@ -2118,46 +2118,46 @@
         <v>32</v>
       </c>
       <c r="L8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="N8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="O8" t="s">
         <v>81</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>82</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="14.25" customHeight="1">
       <c r="A9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="C9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="E9" s="9">
         <v>46452</v>
       </c>
       <c r="F9" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="G9" s="4">
         <f t="shared" si="0"/>
@@ -2172,10 +2172,10 @@
         <v>منخفضة</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="14.25" customHeight="1">
@@ -2183,20 +2183,20 @@
         <v>18</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E10" s="10">
         <v>46351</v>
       </c>
       <c r="F10" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="G10" s="4">
         <f t="shared" si="0"/>
@@ -2204,57 +2204,57 @@
       </c>
       <c r="H10" s="6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ساري</v>
+        <v>قريب</v>
       </c>
       <c r="I10" s="6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>منخفضة</v>
+        <v>متوسطة</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>21</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="N10" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="O10" t="s">
         <v>90</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="P10" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>40</v>
+      </c>
+      <c r="R10" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="O10" t="s">
-        <v>91</v>
-      </c>
-      <c r="P10" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>41</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="14.25" customHeight="1">
       <c r="A11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="C11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="E11" s="10">
         <v>46469</v>
       </c>
       <c r="F11" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="0"/>
@@ -2269,10 +2269,10 @@
         <v>منخفضة</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1">
@@ -2280,20 +2280,20 @@
         <v>18</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E12" s="10">
         <v>46419</v>
       </c>
       <c r="F12" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" ref="G12" si="3">IF(E12="","",E12-30)</f>
@@ -2312,25 +2312,25 @@
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="N12" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="O12" t="s">
         <v>99</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="P12" t="s">
         <v>151</v>
-      </c>
-      <c r="O12" t="s">
-        <v>100</v>
-      </c>
-      <c r="P12" t="s">
-        <v>152</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
       </c>
       <c r="R12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1">
@@ -2338,20 +2338,20 @@
         <v>18</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="E13" s="10">
         <v>46419</v>
       </c>
       <c r="F13" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="0"/>
@@ -2370,25 +2370,25 @@
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="N13" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="O13" t="s">
         <v>99</v>
       </c>
-      <c r="N13" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>40</v>
+      </c>
+      <c r="R13" t="s">
         <v>100</v>
-      </c>
-      <c r="P13" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>41</v>
-      </c>
-      <c r="R13" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1">
@@ -2396,20 +2396,20 @@
         <v>18</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="D14" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E14" s="10">
         <v>46391</v>
       </c>
       <c r="F14" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="0"/>
@@ -2430,25 +2430,25 @@
         <v>32</v>
       </c>
       <c r="L14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="N14" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O14" t="s">
         <v>103</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>104</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
+        <v>40</v>
+      </c>
+      <c r="R14" t="s">
         <v>105</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>41</v>
-      </c>
-      <c r="R14" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="24.75" customHeight="1">
@@ -2456,20 +2456,20 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" s="10">
         <v>46391</v>
       </c>
       <c r="F15" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="0"/>
@@ -2487,28 +2487,28 @@
         <v>21</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="M15" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N15" s="7" t="s">
+      <c r="O15" t="s">
         <v>109</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>110</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
+        <v>40</v>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>41</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1">
@@ -2516,20 +2516,20 @@
         <v>18</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="E16" s="10">
         <v>46396</v>
       </c>
       <c r="F16" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="0"/>
@@ -2550,46 +2550,46 @@
         <v>32</v>
       </c>
       <c r="L16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="N16" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="O16" t="s">
         <v>118</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>119</v>
-      </c>
-      <c r="P16" t="s">
-        <v>120</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="14.25" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="10">
         <v>46535</v>
       </c>
       <c r="F17" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="0"/>
@@ -2604,31 +2604,31 @@
         <v>منخفضة</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E18" s="10">
         <v>46554</v>
       </c>
       <c r="F18" s="5">
         <f ca="1">Tracker_All[[#This Row],[تاريخ الانتهاء]]-TODAY()</f>
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="0"/>
@@ -2643,10 +2643,10 @@
         <v>منخفضة</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="14.25" customHeight="1">
@@ -2654,20 +2654,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E19" s="10">
         <v>46398</v>
       </c>
       <c r="F19" s="5">
         <f ca="1">E19-TODAY()</f>
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="0"/>
@@ -2693,20 +2693,20 @@
         <v>18</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="D20" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E20" s="9">
         <v>46526</v>
       </c>
       <c r="F20" s="5">
         <f ca="1">E20-TODAY()</f>
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="0"/>
@@ -2727,46 +2727,46 @@
         <v>32</v>
       </c>
       <c r="L20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M20" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M20" s="7" t="s">
-        <v>80</v>
-      </c>
       <c r="N20" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="O20" t="s">
+        <v>81</v>
+      </c>
+      <c r="P20" t="s">
         <v>131</v>
-      </c>
-      <c r="O20" t="s">
-        <v>82</v>
-      </c>
-      <c r="P20" t="s">
-        <v>132</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="14.25" customHeight="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="37.5">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="E21" s="4">
         <v>46599</v>
       </c>
       <c r="F21" s="5">
         <f ca="1">E21-TODAY()</f>
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" ref="G21" si="5">IF(E21="","",E21-30)</f>
@@ -2785,22 +2785,22 @@
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
       </c>
       <c r="R21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2828,7 +2828,7 @@
     <row r="2" spans="1:2" ht="14.25" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1">
@@ -2837,42 +2837,42 @@
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1">
       <c r="A4" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>134</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>136</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1">
       <c r="A6" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>138</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>140</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1">
       <c r="A8" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>142</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1">
@@ -2882,7 +2882,7 @@
     <row r="10" spans="1:2" ht="14.25" customHeight="1">
       <c r="A10" s="13"/>
       <c r="B10" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1">
@@ -2892,7 +2892,7 @@
     <row r="12" spans="1:2" ht="14.25" customHeight="1">
       <c r="A12" s="13"/>
       <c r="B12" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1">
@@ -2902,7 +2902,7 @@
     <row r="14" spans="1:2" ht="14.25" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.25" customHeight="1">
@@ -2912,21 +2912,21 @@
     <row r="16" spans="1:2" ht="14.25" customHeight="1">
       <c r="A16" s="13"/>
       <c r="B16" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="E19" s="9">
         <v>46529</v>
@@ -2948,24 +2948,24 @@
         <v>#VALUE!</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1">
       <c r="A20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E20" s="10">
         <v>46215</v>
@@ -2987,10 +2987,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="J20" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
